--- a/aukro/data aukro.xlsx
+++ b/aukro/data aukro.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tereza Hofrichterová\Documents\aukro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tereza Hofrichterová\Documents\CERGE-EI\Other computers\Moje PC\CERGE-EI\Research\platforms\aukro\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,63 +24,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>category</t>
   </si>
   <si>
-    <t>3rd-party ads</t>
-  </si>
-  <si>
-    <t>Promo / internal banners</t>
-  </si>
-  <si>
-    <t>Sticky distractions</t>
-  </si>
-  <si>
-    <t>Interruptions in listing stream</t>
-  </si>
-  <si>
-    <t>Distracting viewport area (%)</t>
-  </si>
-  <si>
-    <t>Fee % (Soukromý)</t>
-  </si>
-  <si>
-    <t>Fee % (Podnikatel)</t>
-  </si>
-  <si>
-    <t>hudební nástroje</t>
-  </si>
-  <si>
-    <t>mobily Xiaomi</t>
-  </si>
-  <si>
-    <t>letní pneu</t>
-  </si>
-  <si>
-    <t>aku naradi</t>
-  </si>
-  <si>
-    <t>MTB kola</t>
-  </si>
-  <si>
-    <t>Společenské a deskové hry</t>
-  </si>
-  <si>
-    <t>kytary</t>
-  </si>
-  <si>
-    <t>knižní detektivky</t>
-  </si>
-  <si>
-    <t>dámské tenisky</t>
-  </si>
-  <si>
-    <t>pánské hodinky</t>
-  </si>
-  <si>
-    <t>zlaté mince po 2011</t>
+    <t>complexity</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>third_party</t>
+  </si>
+  <si>
+    <t>banners</t>
+  </si>
+  <si>
+    <t>sticky</t>
+  </si>
+  <si>
+    <t>viewport_area</t>
+  </si>
+  <si>
+    <t>interruption</t>
+  </si>
+  <si>
+    <t>fee_private</t>
+  </si>
+  <si>
+    <t>fee_business</t>
+  </si>
+  <si>
+    <t>Xiaomi smartphones</t>
+  </si>
+  <si>
+    <t>summer tires</t>
+  </si>
+  <si>
+    <t>cordless power tools</t>
+  </si>
+  <si>
+    <t>mountain bikes</t>
+  </si>
+  <si>
+    <t>board games</t>
+  </si>
+  <si>
+    <t>guitars</t>
+  </si>
+  <si>
+    <t>detective novels</t>
+  </si>
+  <si>
+    <t>sneakers (women)</t>
+  </si>
+  <si>
+    <t>watches (men)</t>
+  </si>
+  <si>
+    <t>investment golden coins</t>
   </si>
 </sst>
 </file>
@@ -412,93 +421,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1575.39</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="I2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1551.62</v>
+      </c>
+      <c r="G3" s="2">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H3" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>34</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1547.33</v>
-      </c>
-      <c r="G2" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2">
-        <v>39</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1575.39</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2">
         <v>40</v>
@@ -507,47 +528,53 @@
         <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2">
-        <v>1551.62</v>
+        <v>1531.41</v>
       </c>
       <c r="G4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>40</v>
       </c>
       <c r="D5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2">
-        <v>1531.41</v>
+        <v>1576.53</v>
       </c>
       <c r="G5" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
         <v>28</v>
@@ -559,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2">
-        <v>1576.53</v>
+        <v>1541.25</v>
       </c>
       <c r="G6" s="2">
         <v>7</v>
@@ -570,91 +597,103 @@
       <c r="H6" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
         <v>28</v>
       </c>
       <c r="C7" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2">
-        <v>1541.25</v>
+        <v>1578.01</v>
       </c>
       <c r="G7" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="H7" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7.5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
       </c>
       <c r="E8" s="2">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>1578.01</v>
+        <v>1510.46</v>
       </c>
       <c r="G8" s="2">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1578.35</v>
+      </c>
+      <c r="G9" s="2">
+        <v>8</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="2">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1510.46</v>
-      </c>
-      <c r="G9" s="2">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2">
         <v>40</v>
@@ -663,10 +702,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2">
-        <v>1578.35</v>
+        <v>1570.91</v>
       </c>
       <c r="G10" s="2">
         <v>8</v>
@@ -674,57 +713,37 @@
       <c r="H10" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F11" s="2">
-        <v>1570.91</v>
+        <v>1568.61</v>
       </c>
       <c r="G11" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2">
-        <v>32</v>
-      </c>
-      <c r="C12" s="2">
-        <v>41</v>
-      </c>
-      <c r="D12" s="2">
-        <v>6</v>
-      </c>
-      <c r="E12" s="2">
-        <v>22</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1568.61</v>
-      </c>
-      <c r="G12" s="2">
         <v>2</v>
       </c>
-      <c r="H12" s="2">
-        <v>2</v>
+      <c r="I11" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/aukro/data aukro.xlsx
+++ b/aukro/data aukro.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tereza Hofrichterová\Documents\CERGE-EI\Other computers\Moje PC\CERGE-EI\Research\platforms\aukro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tbury\Documents\CERGE-EI\Research\platforms\platforms\aukro\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21301EB-C8DC-4D90-9653-5FE6DE1C2847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8976"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>category</t>
   </si>
@@ -90,12 +91,15 @@
   </si>
   <si>
     <t>investment golden coins</t>
+  </si>
+  <si>
+    <t>complexity_index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -133,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +145,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -420,14 +425,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +460,11 @@
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -484,8 +492,11 @@
       <c r="I2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="3">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -513,8 +524,11 @@
       <c r="I3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J3" s="3">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -542,8 +556,11 @@
       <c r="I4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="3">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -571,8 +588,11 @@
       <c r="I5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="3">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -600,8 +620,11 @@
       <c r="I6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="3">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -629,8 +652,11 @@
       <c r="I7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="3">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -658,8 +684,11 @@
       <c r="I8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="3">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -687,8 +716,11 @@
       <c r="I9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="3">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -716,8 +748,11 @@
       <c r="I10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -744,6 +779,9 @@
       </c>
       <c r="I11" t="s">
         <v>4</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/aukro/data aukro.xlsx
+++ b/aukro/data aukro.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tbury\Documents\CERGE-EI\Research\platforms\platforms\aukro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tereza Hofrichterová\Documents\CERGE-EI\Other computers\Moje PC\CERGE-EI\Research\platforms\aukro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21301EB-C8DC-4D90-9653-5FE6DE1C2847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -99,7 +98,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -425,14 +424,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,8 +463,9 @@
       <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -495,8 +496,9 @@
       <c r="J2" s="3">
         <v>2.67</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -527,8 +529,9 @@
       <c r="J3" s="3">
         <v>3.33</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -560,7 +563,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -592,7 +595,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -624,7 +627,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -656,7 +659,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -688,7 +691,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -720,7 +723,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -752,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
